--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
         </is>
       </c>
     </row>
@@ -723,60 +723,64 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +794,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +842,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +852,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +909,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +945,907 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -753,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -780,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -829,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -862,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -895,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -983,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1010,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1164,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1175,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1236,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1260,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1397,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1502,13 +1526,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1619,7 +1647,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1730,7 +1758,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1738,22 +1766,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1786,12 +1814,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1840,12 +1868,801 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>86.0</t>
         </is>
       </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>1/9</t>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>5/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -1108,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,17 +1169,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1185,13 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1708,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1819,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1934,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1988,7 +1996,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/12</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2103,7 +2111,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2386,7 +2394,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2430,13 +2438,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2509,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2551,7 +2563,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1237,24 +1237,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1457,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,37 +1518,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1572,32 +1576,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1605,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,33 +1637,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1683,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -1716,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1827,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1866,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1881,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1981,7 +2001,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1996,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2096,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2111,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2172,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2222,7 +2242,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2333,7 +2353,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2414,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2448,7 +2468,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2529,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2558,12 +2578,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2674,7 +2694,1030 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1814,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,17 +1875,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1891,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,32 +2274,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -2303,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2327,33 +2335,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2381,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2414,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2438,17 +2454,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2458,7 +2474,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2468,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2496,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2529,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2553,37 +2573,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2611,32 +2631,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -2644,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2668,33 +2692,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2722,32 +2750,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2755,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2779,33 +2811,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2833,32 +2869,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2866,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2890,33 +2930,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3127,7 +3171,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3142,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3257,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3362,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3372,7 +3416,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3487,7 +3531,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3602,7 +3646,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3707,17 +3751,818 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>79.0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
         <is>
           <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,18 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2350,7 +2354,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2549,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2668,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2787,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2906,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,32 +2992,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3021,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,33 +3053,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3099,32 +3111,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3132,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3156,17 +3172,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3176,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3214,32 +3230,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3247,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3271,17 +3291,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3291,17 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3329,32 +3349,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3362,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3386,37 +3410,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3516,7 +3540,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3531,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3646,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3746,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3822,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3861,7 +3885,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3937,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3976,7 +4000,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4048,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4317,7 +4341,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4393,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4437,17 +4461,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4566,6 +4590,807 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,13 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,14 +2477,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>83.0</t>
@@ -2488,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2607,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3083,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3192,17 +3196,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3429,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3440,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3583,32 +3587,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3616,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,17 +3648,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3660,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3813,32 +3821,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -3846,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,17 +3882,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3890,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3928,32 +3940,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3961,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,17 +4001,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4005,13 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4154,32 +4174,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4187,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,37 +4235,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4293,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -4302,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4326,17 +4354,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4346,17 +4374,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4384,32 +4412,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4417,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4441,17 +4473,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4461,17 +4493,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4499,32 +4531,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4532,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4556,37 +4592,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4614,32 +4650,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -4647,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4671,17 +4711,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4691,17 +4731,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4802,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4816,7 +4856,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4916,7 +4956,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4931,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4992,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5036,13 +5076,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB39" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5147,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5142,7 +5186,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5157,7 +5201,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5262,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5262,17 +5306,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5333,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5377,17 +5421,703 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>1/14</t>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1785,12 +1785,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4374,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4660,24 +4660,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4736,12 +4736,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4769,32 +4769,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4802,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4826,17 +4830,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4846,17 +4850,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4971,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4999,32 +5003,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5032,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5056,17 +5064,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5076,7 +5084,7 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5114,32 +5122,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5147,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5171,17 +5183,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5191,17 +5203,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5229,32 +5241,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -5262,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5286,17 +5302,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5306,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5344,32 +5360,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -5377,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5401,37 +5421,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5459,32 +5479,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5492,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5516,17 +5540,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5536,12 +5560,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5607,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5646,7 +5670,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5661,7 +5685,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5746,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5776,7 +5800,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5861,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5876,7 +5900,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5948,7 +5972,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5992,17 +6016,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6063,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6121,6 +6145,577 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5489,12 +5489,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5598,32 +5598,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,17 +5659,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5675,17 +5679,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5713,32 +5717,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5746,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5770,17 +5778,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5790,12 +5798,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5861,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5972,7 +5980,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6087,7 +6095,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6141,7 +6149,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6210,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6317,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,7 +6440,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6476,17 +6484,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6547,7 +6555,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6601,7 +6609,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6609,22 +6617,22 @@
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6657,12 +6665,12 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6701,16 +6709,131 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr"/>
-      <c r="AC53" s="2" t="inlineStr">
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>—/15</t>
         </is>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,22 +2009,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,17 +2477,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,22 +5198,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5727,24 +5727,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5836,32 +5836,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5893,17 +5897,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5913,13 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5955,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5980,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6004,37 +6016,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6062,32 +6074,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6095,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6119,32 +6135,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6210,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6325,7 +6341,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6364,7 +6380,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6379,7 +6395,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6440,7 +6456,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6494,7 +6510,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6555,7 +6571,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6609,7 +6625,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6686,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6724,7 +6740,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6801,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6829,13 +6845,477 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB54" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,22 +1656,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5679,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5965,24 +5965,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,32 +6193,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6250,37 +6254,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6308,32 +6312,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6341,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6365,17 +6373,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6385,17 +6393,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -6423,32 +6431,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6456,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6480,17 +6492,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6500,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6538,32 +6550,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6571,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6595,37 +6611,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6725,7 +6741,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6768,32 +6784,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -6801,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6825,17 +6845,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6845,17 +6865,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6970,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7031,7 +7051,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7146,7 +7166,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7195,12 +7215,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -7208,22 +7228,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7256,12 +7276,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7275,47 +7295,737 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>15/15</t>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,14 +2834,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,22 +3072,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,17 +3429,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,14 +4488,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,14 +4607,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,22 +4960,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,22 +5079,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,17 +5198,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,14 +5555,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,17 +6393,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6572,12 +6572,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,32 +6669,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,17 +6730,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6746,12 +6750,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6794,12 +6798,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
@@ -6821,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6860,22 +6864,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6903,32 +6907,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6936,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6960,37 +6968,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7018,32 +7026,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7051,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7075,27 +7087,27 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7133,32 +7145,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7166,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7190,32 +7206,32 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7248,32 +7264,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7281,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7305,37 +7325,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7363,32 +7383,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7396,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7420,17 +7444,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7440,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7511,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7550,7 +7574,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7626,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7741,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7856,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7971,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8015,17 +8039,1167 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB64" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr">
-        <is>
-          <t>11/15</t>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,17 +1418,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,22 +1775,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,17 +3072,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,17 +3310,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,22 +3544,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,22 +4131,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,22 +4726,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4960,17 +4960,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,22 +5674,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5793,17 +5793,17 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6507,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,17 +6626,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6983,17 +6983,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7502,32 +7502,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7559,17 +7563,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7579,12 +7583,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7617,32 +7621,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -7650,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,37 +7682,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7740,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -7765,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,32 +7801,32 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7847,32 +7859,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7880,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7904,37 +7920,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7962,32 +7978,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7995,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8019,37 +8039,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8077,32 +8097,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8110,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8134,37 +8158,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8225,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8264,7 +8288,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8307,32 +8331,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8340,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8364,32 +8392,32 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8455,7 +8483,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8570,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8685,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8800,7 +8828,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8915,7 +8943,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9030,7 +9058,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9084,7 +9112,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9145,7 +9173,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9189,17 +9217,937 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>89.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>80.7</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>4/15</t>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>82.7</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,17 +2009,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,22 +2239,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,22 +2358,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,17 +3429,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,22 +4016,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,22 +4369,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,12 +4612,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,22 +5079,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,17 +5198,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,22 +5317,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,22 +5436,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6031,17 +6031,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6388,17 +6388,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6993,7 +6993,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,22 +7340,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,17 +7459,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7578,22 +7578,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,22 +7697,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8216,32 +8216,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8249,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,17 +8277,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8293,12 +8297,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8341,24 +8345,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8368,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8417,7 +8421,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8483,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8522,7 +8526,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8598,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,7 +8641,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8680,32 +8684,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -8713,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8737,32 +8745,32 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
@@ -8828,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8867,7 +8875,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8910,32 +8918,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8943,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8967,37 +8979,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9097,7 +9109,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9112,7 +9124,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9140,32 +9152,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -9173,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9197,37 +9213,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9255,32 +9271,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -9288,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9312,32 +9332,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9370,32 +9390,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -9403,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9427,37 +9451,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9633,7 +9657,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9672,7 +9696,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9748,7 +9772,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9802,7 +9826,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9863,7 +9887,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9907,12 +9931,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9978,7 +10002,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10040,22 +10064,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10088,12 +10112,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10107,47 +10131,1197 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="W83" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X83" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y83" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>88.2</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
         <is>
           <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,17 +1303,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2368,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4131,17 +4131,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,17 +7935,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9281,12 +9281,12 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9357,7 +9357,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9400,12 +9400,12 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9509,32 +9509,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9542,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9566,32 +9570,32 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9624,32 +9628,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9657,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9681,17 +9689,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9701,12 +9709,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9772,7 +9780,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10002,7 +10010,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10041,7 +10049,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10117,7 +10125,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10232,7 +10240,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10347,7 +10355,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10462,7 +10470,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10577,7 +10585,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10692,7 +10700,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10807,7 +10815,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10922,7 +10930,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11037,7 +11045,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11086,7 +11094,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11152,7 +11160,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11201,12 +11209,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11267,7 +11275,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11311,17 +11319,247 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB92" s="2" t="inlineStr">
-        <is>
-          <t>86.5</t>
-        </is>
-      </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>12/15</t>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3778,17 +3778,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4845,17 +4845,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7826,7 +7826,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,12 +8059,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8641,17 +8641,17 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9638,24 +9638,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:52</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9747,32 +9747,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -9780,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9804,27 +9808,27 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
@@ -9895,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9977,32 +9981,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -10010,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10034,17 +10042,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10054,12 +10062,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10092,32 +10100,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -10125,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10149,17 +10161,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10169,17 +10181,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10207,32 +10219,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10240,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10264,32 +10280,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10355,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10470,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10509,7 +10525,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10700,7 +10716,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10739,7 +10755,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10815,7 +10831,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10930,7 +10946,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10969,7 +10985,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11045,7 +11061,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11160,7 +11176,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11275,7 +11291,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11324,7 +11340,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11390,7 +11406,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11452,22 +11468,22 @@
       <c r="A94" s="2" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -11500,12 +11516,12 @@
       <c r="M94" s="2" t="inlineStr"/>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11519,47 +11535,622 @@
       <c r="T94" s="2" t="inlineStr"/>
       <c r="U94" s="2" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>19:40</t>
         </is>
       </c>
-      <c r="V94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W94" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X94" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y94" s="2" t="inlineStr">
+      <c r="Y96" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z94" s="2" t="inlineStr">
+      <c r="Z96" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA94" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB94" s="2" t="inlineStr">
-        <is>
-          <t>84.5</t>
-        </is>
-      </c>
-      <c r="AC94" s="2" t="inlineStr">
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
         <is>
           <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,17 +2244,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2363,17 +2363,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,12 +3668,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,17 +4021,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,12 +4493,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4855,7 +4855,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5084,17 +5084,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,17 +5441,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6155,17 +6155,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,17 +6274,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6631,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6864,7 +6864,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7107,17 +7107,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7345,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,12 +7583,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7702,17 +7702,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7821,17 +7821,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7940,17 +7940,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8069,7 +8069,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -8602,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8999,17 +8999,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9114,17 +9114,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9352,12 +9352,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9471,17 +9471,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9590,17 +9590,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,17 +9709,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10072,7 +10072,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10229,24 +10229,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10453,32 +10453,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10486,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10510,17 +10514,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10530,12 +10534,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10683,32 +10687,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10716,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10740,17 +10748,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10760,17 +10768,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10798,32 +10806,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10831,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10855,17 +10867,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10875,17 +10887,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10913,32 +10925,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -10946,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10970,17 +10986,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -10990,12 +11006,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11028,32 +11044,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11061,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11085,17 +11105,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11105,12 +11125,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11143,32 +11163,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:01</t>
@@ -11176,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11200,17 +11224,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11220,17 +11244,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11258,32 +11282,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11291,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11315,17 +11343,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11335,17 +11363,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11373,32 +11401,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11406,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11430,17 +11462,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11450,17 +11482,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11521,7 +11553,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11575,7 +11607,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11636,7 +11668,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11685,7 +11717,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11751,7 +11783,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11795,12 +11827,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11866,7 +11898,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11920,7 +11952,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11928,22 +11960,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -11976,12 +12008,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -11995,7 +12027,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12030,12 +12062,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -12043,22 +12075,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A53893D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12091,12 +12123,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12110,47 +12142,507 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
         <is>
           <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1666,12 +1666,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,17 +3549,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,17 +4255,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4374,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,17 +4731,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5322,17 +5322,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5679,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5917,17 +5917,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6512,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6750,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7896,7 +7896,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7945,12 +7945,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8059,17 +8059,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,17 +8178,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8656,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8999,12 +8999,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,17 +9233,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9595,12 +9595,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9828,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,17 +9943,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10018,7 +10018,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10062,17 +10062,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10181,17 +10181,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,12 +10768,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11006,17 +11006,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11292,24 +11292,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11368,12 +11368,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -11411,24 +11411,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11487,12 +11487,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11520,32 +11520,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11553,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11577,17 +11581,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11597,17 +11601,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11726,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11865,32 +11869,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11898,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11922,17 +11930,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11942,17 +11950,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -11980,32 +11988,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12013,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12037,17 +12049,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12057,17 +12069,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12107,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>12:01</t>
@@ -12128,7 +12144,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12152,17 +12168,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12172,17 +12188,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -12210,32 +12226,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -12243,7 +12263,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12267,17 +12287,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12287,12 +12307,12 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12325,32 +12345,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>08:21</t>
@@ -12358,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12382,17 +12406,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12402,17 +12426,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -12473,7 +12497,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12517,17 +12541,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12588,7 +12612,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12632,17 +12656,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2725,12 +2725,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5560,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8253,7 +8253,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,17 +8297,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9238,12 +9238,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,17 +9943,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12069,17 +12069,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12355,24 +12355,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12431,12 +12431,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12464,32 +12464,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12497,7 +12501,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12521,17 +12525,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12541,17 +12545,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12616,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">

--- a/data/export/2026-10-24-浦东78路.xlsx
+++ b/data/export/2026-10-24-浦东78路.xlsx
@@ -5873,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
